--- a/Codelist Excel Files and Conversion Templates to XML/terminationOutcome.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/terminationOutcome.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="9200" yWindow="3280" windowWidth="39400" windowHeight="24940" tabRatio="500" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="DictionaryName" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Definitions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="AssociatedElements" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="AlternateNames" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Lists" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DictionaryName" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AssociatedElements" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AlternateNames" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -995,7 +995,7 @@
       <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1139,7 +1139,31 @@
         <f>IF(ISNA(VLOOKUP(B4,AssociatedElements!B$2:B2942,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
-      <c r="G4" s="9" t="n"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>stopped_short</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Stopped short of design depth</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Installation stopped before the design toe depth was reached without the refusal criterion being met - for example on an obstruction or an instruction. Neither design_depth nor refusal applies; the reason belongs in a construction event or a remark.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>DIGGS</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2">
@@ -1595,7 +1619,16 @@
         <f>IF(ISNA(VLOOKUP(B4,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B4" s="2" t="n"/>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>stopped_short</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>//diggs:RIColumnConstruction/diggs:terminationOutcome</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5">
